--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_42.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2654759.8840925</v>
+        <v>2647892.891143844</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.410716289646</v>
+        <v>286.4107162900655</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.410716289646</v>
+        <v>286.4107162900655</v>
       </c>
     </row>
     <row r="11">
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -742,19 +742,19 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>192.3498461705186</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>308.4311513056531</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S5" t="n">
         <v>94.84816780232291</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>258.8995092302829</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1027,19 +1027,19 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>288.1827411620896</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1091,13 +1091,13 @@
         <v>240.445564079015</v>
       </c>
       <c r="P7" t="n">
-        <v>287.4478973282775</v>
+        <v>285.8567266822216</v>
       </c>
       <c r="Q7" t="n">
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>294.7033291544482</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>66.5639999646113</v>
+        <v>215.2520250048122</v>
       </c>
       <c r="T9" t="n">
         <v>5.357765217513816</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751173017</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1380,13 +1380,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H11" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V12" t="n">
         <v>64.51066719152016</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
@@ -1690,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1735,10 +1735,10 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429562</v>
       </c>
       <c r="U15" t="n">
-        <v>50.21035976018675</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V15" t="n">
         <v>64.51066719152016</v>
@@ -1857,10 +1857,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H17" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
         <v>11.09991244551929</v>
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H18" t="n">
-        <v>62.67776252544251</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H20" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>144.8481678023229</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2200,10 +2200,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>197.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S21" t="n">
         <v>116.5639999646113</v>
@@ -2334,7 +2334,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2398,19 +2398,19 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>73.04152018756569</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>239.5984974349628</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.55655664632661</v>
+        <v>104.5622219498565</v>
       </c>
       <c r="C27" t="n">
         <v>11.09991244551929</v>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2680,7 +2680,7 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T27" t="n">
         <v>55.35776521751382</v>
@@ -2695,7 +2695,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X27" t="n">
-        <v>132.54050197083</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y27" t="n">
         <v>49.39139276613435</v>
@@ -2802,13 +2802,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H29" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2872,19 +2872,19 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2929,7 +2929,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>155.4146630973942</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X30" t="n">
         <v>69.86273944538755</v>
@@ -3045,7 +3045,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I32" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T32" t="n">
         <v>236.6755817285639</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>11.09991244551929</v>
+        <v>73.77767497096181</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3160,10 +3160,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U33" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V33" t="n">
-        <v>127.1884297169626</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W33" t="n">
         <v>82.37314290982852</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>288.3734759809475</v>
+        <v>292.3388673663621</v>
       </c>
       <c r="X35" t="n">
         <v>242.2818334606677</v>
@@ -3343,7 +3343,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>84.14143263308497</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3352,13 +3352,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3634,7 +3634,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>289.8088571951495</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>49.39139276613435</v>
+        <v>244.9427694002283</v>
       </c>
     </row>
     <row r="40">
@@ -3744,7 +3744,7 @@
         <v>60.33915573984979</v>
       </c>
       <c r="E41" t="n">
-        <v>54.36328960686865</v>
+        <v>58.32868099228319</v>
       </c>
       <c r="F41" t="n">
         <v>54.88962870801186</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3880,7 +3880,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>150.372414784409</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3990,7 +3990,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T44" t="n">
         <v>236.6755817285639</v>
@@ -4051,19 +4051,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>99.29663227406654</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4330,16 +4330,16 @@
         <v>411.95</v>
       </c>
       <c r="M2" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="N2" t="n">
+        <v>411.95</v>
+      </c>
+      <c r="O2" t="n">
         <v>793.1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>1174.25</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1540</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1540</v>
       </c>
       <c r="Q2" t="n">
         <v>1540</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4385,16 +4385,16 @@
         <v>897.189519579215</v>
       </c>
       <c r="E3" t="n">
-        <v>897.189519579215</v>
+        <v>702.8967456696003</v>
       </c>
       <c r="F3" t="n">
-        <v>897.189519579215</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G3" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4455,25 +4455,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1205.547976938917</v>
+        <v>735.5658222069326</v>
       </c>
       <c r="C4" t="n">
-        <v>1205.547976938917</v>
+        <v>861.5678280253684</v>
       </c>
       <c r="D4" t="n">
-        <v>1318.867121063917</v>
+        <v>974.8869721503685</v>
       </c>
       <c r="E4" t="n">
-        <v>1318.867121063917</v>
+        <v>1092.715876361782</v>
       </c>
       <c r="F4" t="n">
-        <v>1318.867121063917</v>
+        <v>1217.076848953717</v>
       </c>
       <c r="G4" t="n">
-        <v>1318.867121063917</v>
+        <v>1370.483414840602</v>
       </c>
       <c r="H4" t="n">
-        <v>1318.867121063917</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
         <v>1540</v>
@@ -4506,25 +4506,25 @@
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>30.8</v>
       </c>
       <c r="V4" t="n">
-        <v>701.4985197772105</v>
+        <v>189.4774745777372</v>
       </c>
       <c r="W4" t="n">
-        <v>873.3894380368879</v>
+        <v>361.3683928374146</v>
       </c>
       <c r="X4" t="n">
-        <v>1024.420229061081</v>
+        <v>512.3991838616081</v>
       </c>
       <c r="Y4" t="n">
-        <v>1135.829529740114</v>
+        <v>623.8084845406404</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
         <v>30.8</v>
@@ -4567,43 +4567,43 @@
         <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>793.1</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="P5" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
       </c>
       <c r="R5" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>395.5473863086054</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="C6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="D6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="E6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="F6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="G6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="H6" t="n">
-        <v>30.8</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4661,28 +4661,28 @@
         <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>924.7177645803712</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>857.4814009797537</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>852.069516921659</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>851.8570323154097</v>
+        <v>575.9338724144908</v>
       </c>
       <c r="V6" t="n">
-        <v>837.1997927280156</v>
+        <v>561.2766328270967</v>
       </c>
       <c r="W6" t="n">
-        <v>804.4996483746535</v>
+        <v>270.182954885592</v>
       </c>
       <c r="X6" t="n">
-        <v>784.4362751974943</v>
+        <v>250.1195817084329</v>
       </c>
       <c r="Y6" t="n">
-        <v>395.5473863086054</v>
+        <v>250.1195817084329</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>404.9974293695179</v>
+        <v>1210.336612312233</v>
       </c>
       <c r="C7" t="n">
-        <v>530.9994351879537</v>
+        <v>1336.338618130668</v>
       </c>
       <c r="D7" t="n">
-        <v>644.3185793129538</v>
+        <v>1449.657762255669</v>
       </c>
       <c r="E7" t="n">
-        <v>762.1474835243669</v>
+        <v>1540</v>
       </c>
       <c r="F7" t="n">
-        <v>886.5084561163023</v>
+        <v>1540</v>
       </c>
       <c r="G7" t="n">
-        <v>1039.915022003188</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
-        <v>1209.431607162585</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1430.564486098668</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
         <v>1540</v>
@@ -4734,10 +4734,10 @@
         <v>978.5758798878493</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
@@ -4746,22 +4746,22 @@
         <v>30.8</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>30.8</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="V7" t="n">
-        <v>30.8</v>
+        <v>664.2482646830374</v>
       </c>
       <c r="W7" t="n">
-        <v>30.8</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="X7" t="n">
-        <v>181.8307910241935</v>
+        <v>987.1699739669083</v>
       </c>
       <c r="Y7" t="n">
-        <v>293.2400917032258</v>
+        <v>1098.579274645941</v>
       </c>
     </row>
     <row r="8">
@@ -4795,25 +4795,25 @@
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M8" t="n">
         <v>411.95</v>
       </c>
-      <c r="K8" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="L8" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="M8" t="n">
-        <v>793.1</v>
-      </c>
       <c r="N8" t="n">
-        <v>1174.25</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>359.8298342171994</v>
+        <v>746.9995952961838</v>
       </c>
       <c r="C9" t="n">
-        <v>359.8298342171994</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D9" t="n">
-        <v>359.8298342171994</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>359.8298342171994</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>359.8298342171994</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
         <v>30.8</v>
@@ -4898,28 +4898,28 @@
         <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>888.5522899094971</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>821.3159263088796</v>
+        <v>820.0447210784432</v>
       </c>
       <c r="T9" t="n">
-        <v>815.9040422507849</v>
+        <v>814.6328370203485</v>
       </c>
       <c r="U9" t="n">
-        <v>815.6915576445356</v>
+        <v>814.4203524140992</v>
       </c>
       <c r="V9" t="n">
-        <v>801.0343180571415</v>
+        <v>799.7631128267051</v>
       </c>
       <c r="W9" t="n">
-        <v>768.3341737037794</v>
+        <v>767.0629684733429</v>
       </c>
       <c r="X9" t="n">
-        <v>748.2708005266202</v>
+        <v>746.9995952961838</v>
       </c>
       <c r="Y9" t="n">
-        <v>748.2708005266202</v>
+        <v>746.9995952961838</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1058.488973253223</v>
+        <v>404.0685093339813</v>
       </c>
       <c r="C10" t="n">
-        <v>1184.490979071659</v>
+        <v>530.0705151524171</v>
       </c>
       <c r="D10" t="n">
-        <v>1297.810123196659</v>
+        <v>643.3896592774172</v>
       </c>
       <c r="E10" t="n">
-        <v>1415.639027408072</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F10" t="n">
-        <v>1540.000000000007</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G10" t="n">
-        <v>1540.000000000007</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H10" t="n">
-        <v>1540.000000000007</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I10" t="n">
-        <v>1540.000000000007</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J10" t="n">
-        <v>1540.000000000007</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000007</v>
+        <v>1540</v>
       </c>
       <c r="L10" t="n">
         <v>1517.821760089168</v>
@@ -4983,22 +4983,22 @@
         <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>67.02804009979491</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>313.5792327380815</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>512.4006256240275</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>684.2915438837049</v>
+        <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>835.3223349078984</v>
+        <v>180.9018709886569</v>
       </c>
       <c r="Y10" t="n">
-        <v>946.7316355869307</v>
+        <v>292.3111716676892</v>
       </c>
     </row>
     <row r="11">
@@ -5023,10 +5023,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
@@ -5035,22 +5035,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L11" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M11" t="n">
-        <v>946.8779417665908</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>2236</v>
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F12" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G12" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5144,19 +5144,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="13">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
@@ -5281,10 +5281,10 @@
         <v>946.8779417665908</v>
       </c>
       <c r="N14" t="n">
-        <v>1500.287941766591</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="O14" t="n">
-        <v>1500.287941766591</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P14" t="n">
         <v>1797.400904947332</v>
@@ -5293,28 +5293,28 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5378,22 +5378,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504074</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5500,31 +5500,31 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106526</v>
       </c>
       <c r="K17" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="L17" t="n">
-        <v>436.0291130376557</v>
+        <v>618.3311712710653</v>
       </c>
       <c r="M17" t="n">
-        <v>946.8779417665908</v>
+        <v>1129.18</v>
       </c>
       <c r="N17" t="n">
-        <v>1500.287941766591</v>
+        <v>1682.59</v>
       </c>
       <c r="O17" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="P17" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C18" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D18" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E18" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F18" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G18" t="n">
-        <v>108.0308712378207</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H18" t="n">
         <v>44.72</v>
@@ -5640,19 +5640,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C19" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D19" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E19" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F19" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G19" t="n">
         <v>1257.463422273695</v>
@@ -5694,22 +5694,22 @@
         <v>44.72</v>
       </c>
       <c r="T19" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C20" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
         <v>44.72</v>
@@ -5743,19 +5743,19 @@
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L20" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M20" t="n">
-        <v>946.8779417665908</v>
+        <v>598.13</v>
       </c>
       <c r="N20" t="n">
-        <v>1243.990904947333</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O20" t="n">
         <v>1243.990904947333</v>
@@ -5767,28 +5767,28 @@
         <v>2236</v>
       </c>
       <c r="R20" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S20" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y20" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="21">
@@ -5798,16 +5798,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>387.7869114524009</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
         <v>44.72</v>
@@ -5843,31 +5843,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X21" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y21" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="22">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C23" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D23" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E23" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F23" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G23" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H23" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I23" t="n">
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M23" t="n">
-        <v>1108.978828728935</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N23" t="n">
-        <v>1662.388828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S23" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X23" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>472.7782575464261</v>
+        <v>297.950717050992</v>
       </c>
       <c r="C24" t="n">
-        <v>461.5662247731743</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="D24" t="n">
-        <v>387.7869114524009</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="E24" t="n">
-        <v>387.7869114524009</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="F24" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="G24" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="H24" t="n">
         <v>44.72</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R24" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S24" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T24" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U24" t="n">
-        <v>776.5100746769283</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V24" t="n">
-        <v>711.3477845844836</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W24" t="n">
-        <v>628.142589726071</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X24" t="n">
-        <v>557.5741660438614</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y24" t="n">
-        <v>507.6838703204934</v>
+        <v>332.8563298250593</v>
       </c>
     </row>
     <row r="25">
@@ -6168,19 +6168,19 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X25" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y25" t="n">
         <v>807.7884919737335</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H26" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6220,22 +6220,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>946.8779417665908</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P26" t="n">
-        <v>2053.697941766591</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,13 +6272,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>55.93203277325181</v>
+        <v>402.0654643105373</v>
       </c>
       <c r="C27" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="D27" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E27" t="n">
         <v>44.72</v>
@@ -6323,25 +6323,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U27" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W27" t="n">
-        <v>274.6072361907174</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X27" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="28">
@@ -6445,10 +6445,10 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G29" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H29" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,16 +6457,16 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L29" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M29" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N29" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O29" t="n">
         <v>1797.400904947332</v>
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>398.9989442256527</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>387.7869114524009</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>387.7869114524009</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E30" t="n">
-        <v>387.7869114524009</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6572,13 +6572,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>554.3632764052976</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>483.794852723088</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>433.9045569997199</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6667,49 +6667,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C32" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D32" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E32" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F32" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G32" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H32" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I32" t="n">
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>64.92117127106526</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>618.3311712710653</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1129.18</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1682.59</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6718,25 +6718,25 @@
         <v>2236</v>
       </c>
       <c r="S32" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T32" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U32" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V32" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W32" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X32" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y32" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="33">
@@ -6746,7 +6746,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C33" t="n">
         <v>44.72</v>
@@ -6803,19 +6803,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="34">
@@ -6904,40 +6904,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C35" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D35" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E35" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F35" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>690.5809049473327</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N35" t="n">
         <v>1797.400904947332</v>
@@ -6967,13 +6967,13 @@
         <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y35" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D36" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E36" t="n">
-        <v>387.7869114524009</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="H36" t="n">
         <v>44.72</v>
@@ -7049,10 +7049,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="37">
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
         <v>1010.366979583462</v>
@@ -7128,10 +7128,10 @@
         <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7165,19 +7165,19 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>1151.54</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N38" t="n">
-        <v>1797.400904947332</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O38" t="n">
         <v>1797.400904947332</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7265,31 +7265,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="40">
@@ -7299,16 +7299,16 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
         <v>1153.55685638681</v>
@@ -7359,16 +7359,16 @@
         <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7387,16 +7387,16 @@
         <v>271.977919889736</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7405,22 +7405,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N41" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>391.4553531635761</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>380.2433203903244</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>380.2433203903244</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E42" t="n">
-        <v>380.2433203903244</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F42" t="n">
-        <v>380.2433203903244</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G42" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7523,10 +7523,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>476.2512616610114</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>426.3609659376434</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7590,16 +7590,16 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
         <v>745.8791912947012</v>
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F44" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G44" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H44" t="n">
         <v>44.72</v>
@@ -7639,22 +7639,22 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>137.1709049473328</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="L44" t="n">
-        <v>1151.54</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="M44" t="n">
         <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P44" t="n">
         <v>1797.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C45" t="n">
-        <v>461.5662247731743</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I45" t="n">
         <v>44.72</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>929.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>439.6923140185369</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>385.2870600406814</v>
       </c>
       <c r="Q2" t="n">
-        <v>172.8226843274854</v>
+        <v>542.2671287719298</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8210,19 +8210,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>542.2671287719298</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,25 +8678,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N11" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>184.4305532057413</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8924,13 +8924,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>370.361973797064</v>
       </c>
       <c r="P14" t="n">
-        <v>300.4011642636528</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121687</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9164,13 +9164,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,22 +9386,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>777.3630622928068</v>
+        <v>570.6337105418884</v>
       </c>
       <c r="O20" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P20" t="n">
         <v>559.2870600406815</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>559</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
-        <v>1036.248958069835</v>
+        <v>734.3719802008219</v>
       </c>
       <c r="O23" t="n">
         <v>629.2478695740924</v>
@@ -9644,7 +9644,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>193.2279078336117</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,7 +9863,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -9878,10 +9878,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q26" t="n">
-        <v>356.9661774925453</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,7 +10100,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10112,7 +10112,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P29" t="n">
         <v>0.2870600406814136</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>55.44822975121687</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10349,13 +10349,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O32" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P32" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
@@ -10583,7 +10583,7 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>734.3719802008218</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>559</v>
       </c>
-      <c r="L38" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M38" t="n">
-        <v>637.6468801143703</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N41" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>128.4277587171436</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>637.6468801143703</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22949,13 +22949,13 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.591170646055843</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646049022</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -26272,7 +26272,7 @@
         <v>1322305.794848944</v>
       </c>
       <c r="C2" t="n">
-        <v>1322305.794848943</v>
+        <v>1322305.794848944</v>
       </c>
       <c r="D2" t="n">
         <v>1322305.794848944</v>
@@ -26284,7 +26284,7 @@
         <v>1322345.892349225</v>
       </c>
       <c r="G2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="H2" t="n">
         <v>1322345.892349225</v>
@@ -26293,10 +26293,10 @@
         <v>1322345.892349225</v>
       </c>
       <c r="J2" t="n">
+        <v>1322345.892349224</v>
+      </c>
+      <c r="K2" t="n">
         <v>1322345.892349225</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1322345.892349224</v>
       </c>
       <c r="L2" t="n">
         <v>1322345.892349225</v>
@@ -26311,7 +26311,7 @@
         <v>1322345.892349224</v>
       </c>
       <c r="P2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636664</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203549</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>558836.0699494345</v>
+        <v>557320.2142611187</v>
       </c>
       <c r="C6" t="n">
-        <v>696414.0500832485</v>
+        <v>694898.1943949329</v>
       </c>
       <c r="D6" t="n">
-        <v>698474.8219955649</v>
+        <v>696958.9663072488</v>
       </c>
       <c r="E6" t="n">
-        <v>374592.4891226891</v>
+        <v>372850.6393095815</v>
       </c>
       <c r="F6" t="n">
-        <v>717783.3844681937</v>
+        <v>716041.5346550863</v>
       </c>
       <c r="G6" t="n">
-        <v>719728.9609363789</v>
+        <v>717987.1111232716</v>
       </c>
       <c r="H6" t="n">
-        <v>721677.2377536803</v>
+        <v>719935.3879405729</v>
       </c>
       <c r="I6" t="n">
-        <v>723628.2343970408</v>
+        <v>721886.3845839332</v>
       </c>
       <c r="J6" t="n">
-        <v>310061.9705986656</v>
+        <v>308320.1207855577</v>
       </c>
       <c r="K6" t="n">
-        <v>727538.4663508849</v>
+        <v>725796.6165377777</v>
       </c>
       <c r="L6" t="n">
-        <v>729497.7419111446</v>
+        <v>727755.8920980368</v>
       </c>
       <c r="M6" t="n">
-        <v>670211.8178071234</v>
+        <v>668469.967994016</v>
       </c>
       <c r="N6" t="n">
-        <v>733424.7148419768</v>
+        <v>731682.8650288695</v>
       </c>
       <c r="O6" t="n">
-        <v>455392.4540997152</v>
+        <v>453650.6042866075</v>
       </c>
       <c r="P6" t="n">
-        <v>737363.0569507253</v>
+        <v>735621.2071376181</v>
       </c>
     </row>
   </sheetData>
@@ -26993,19 +26993,19 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>350</v>
+      </c>
+      <c r="K2" t="n">
         <v>-0</v>
       </c>
-      <c r="J2" t="n">
-        <v>350</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27027,43 +27027,43 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>-0</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>-0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27521,19 +27521,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>150.322251051394</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3083845693742</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27591,28 +27591,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>357.5364742752637</v>
+        <v>400</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
@@ -27642,16 +27642,16 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>359.4505875674658</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27770,7 +27770,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>288.3742880620964</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,19 +27806,19 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>144.1904017477389</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27837,22 +27837,22 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>372.2356904372913</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
-        <v>145.809871968566</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
         <v>288.520773801143</v>
@@ -27882,16 +27882,16 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28001,7 +28001,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28034,10 +28034,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>252.570468137931</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>400</v>
+        <v>251.3119749597991</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28080,19 +28080,19 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28119,19 +28119,19 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
-        <v>246.6185464050405</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>399.0616969338014</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28159,13 +28159,13 @@
         <v>350</v>
       </c>
       <c r="G11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H11" t="n">
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28238,10 +28238,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H12" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28280,7 +28280,7 @@
         <v>350</v>
       </c>
       <c r="U12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
@@ -28469,10 +28469,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28514,10 +28514,10 @@
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>350</v>
+        <v>287.3222374745577</v>
       </c>
       <c r="U15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>350</v>
@@ -28636,10 +28636,10 @@
         <v>350</v>
       </c>
       <c r="H17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,7 +28697,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C18" t="n">
         <v>350</v>
@@ -28712,10 +28712,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H18" t="n">
-        <v>269.4903246609786</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>217.1263858913485</v>
@@ -28791,7 +28791,7 @@
         <v>350</v>
       </c>
       <c r="G19" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="H19" t="n">
         <v>350</v>
@@ -28830,7 +28830,7 @@
         <v>350</v>
       </c>
       <c r="T19" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U19" t="n">
         <v>350</v>
@@ -28873,7 +28873,7 @@
         <v>350</v>
       </c>
       <c r="H20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>350</v>
@@ -28943,10 +28943,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>269.6305770343469</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>325.7395358750273</v>
@@ -28979,10 +28979,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S21" t="n">
         <v>350</v>
@@ -29113,7 +29113,7 @@
         <v>350</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29177,19 +29177,19 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>274.8961667101369</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H24" t="n">
-        <v>332.1680871864211</v>
+        <v>92.56958975145832</v>
       </c>
       <c r="I24" t="n">
         <v>217.1263858913485</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29304,7 +29304,7 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29319,7 +29319,7 @@
         <v>350</v>
       </c>
       <c r="Y25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26">
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>350</v>
+        <v>279.99433469647</v>
       </c>
       <c r="C27" t="n">
         <v>350</v>
@@ -29417,7 +29417,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>339.6362423378769</v>
@@ -29459,7 +29459,7 @@
         <v>350</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T27" t="n">
         <v>350</v>
@@ -29474,7 +29474,7 @@
         <v>350</v>
       </c>
       <c r="X27" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="Y27" t="n">
         <v>350</v>
@@ -29581,13 +29581,13 @@
         <v>350</v>
       </c>
       <c r="G29" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H29" t="n">
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29651,19 +29651,19 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>267.4280115586812</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29708,7 +29708,7 @@
         <v>350</v>
       </c>
       <c r="W30" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="X30" t="n">
         <v>350</v>
@@ -29824,7 +29824,7 @@
         <v>350</v>
       </c>
       <c r="I32" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T32" t="n">
         <v>350</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -29939,10 +29939,10 @@
         <v>350</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V33" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="W33" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30103,7 +30103,7 @@
         <v>350</v>
       </c>
       <c r="W35" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="X35" t="n">
         <v>350</v>
@@ -30122,7 +30122,7 @@
         <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>276.9584798124343</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30131,13 +30131,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>269.4903246609787</v>
       </c>
       <c r="I36" t="n">
         <v>217.1263858913485</v>
@@ -30185,7 +30185,7 @@
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30204,7 +30204,7 @@
         <v>350</v>
       </c>
       <c r="D37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E37" t="n">
         <v>350</v>
@@ -30264,7 +30264,7 @@
         <v>350</v>
       </c>
       <c r="X37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y37" t="n">
         <v>350</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30413,7 +30413,7 @@
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>110.4015025650372</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
     </row>
     <row r="40">
@@ -30447,7 +30447,7 @@
         <v>350</v>
       </c>
       <c r="F40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G40" t="n">
         <v>350</v>
@@ -30495,7 +30495,7 @@
         <v>350</v>
       </c>
       <c r="V40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="W40" t="n">
         <v>350</v>
@@ -30523,7 +30523,7 @@
         <v>350</v>
       </c>
       <c r="E41" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="F41" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30599,7 +30599,7 @@
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>260.9994602472874</v>
       </c>
       <c r="E42" t="n">
         <v>342.6720972219126</v>
@@ -30608,10 +30608,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30659,7 +30659,7 @@
         <v>350</v>
       </c>
       <c r="X42" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30738,7 +30738,7 @@
         <v>350</v>
       </c>
       <c r="X43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="Y43" t="n">
         <v>350</v>
@@ -30769,7 +30769,7 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30802,7 +30802,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T44" t="n">
         <v>350</v>
@@ -30830,19 +30830,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>144.0848657037828</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30851,7 +30851,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -34752,19 +34752,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>385</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>385</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>369.4444444444445</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,28 +34877,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.42267393818508</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -34928,16 +34928,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>160.2802773512497</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
@@ -34989,19 +34989,19 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35123,22 +35123,22 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>91.25478560033478</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>110.5409231326582</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35168,16 +35168,16 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35238,7 +35238,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35366,19 +35366,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35405,19 +35405,19 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>36.59397989878273</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>151.6180515036939</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,25 +35457,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35703,13 +35703,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>300.1141042229716</v>
+      </c>
+      <c r="P14" t="n">
         <v>559</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>300.1141042229714</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612654</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35943,13 +35943,13 @@
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36077,7 +36077,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G19" t="n">
-        <v>104.95612715847</v>
+        <v>97.1674577926042</v>
       </c>
       <c r="H19" t="n">
         <v>121.2288738983814</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U19" t="n">
         <v>199.0416087255421</v>
@@ -36165,22 +36165,22 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M20" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>300.1141042229716</v>
+        <v>93.38475247205321</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P20" t="n">
         <v>559</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>559</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>559</v>
+        <v>257.1230221309867</v>
       </c>
       <c r="O23" t="n">
         <v>559</v>
@@ -36423,7 +36423,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20.40522350612631</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36605,7 +36605,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="26">
@@ -36642,7 +36642,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -36657,10 +36657,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q26" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,7 +36879,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>300.1141042229715</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36891,7 +36891,7 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>20.40522350612654</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37128,13 +37128,13 @@
         <v>559</v>
       </c>
       <c r="O32" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,7 +37350,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
         <v>559</v>
@@ -37362,7 +37362,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37490,7 +37490,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D37" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E37" t="n">
         <v>69.01909516304346</v>
@@ -37550,7 +37550,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
         <v>62.53464715053764</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>559</v>
       </c>
-      <c r="L38" t="n">
-        <v>559.0000000000001</v>
-      </c>
       <c r="M38" t="n">
-        <v>93.38475247205298</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37733,7 +37733,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F40" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
         <v>104.95612715847</v>
@@ -37781,7 +37781,7 @@
         <v>199.0416087255421</v>
       </c>
       <c r="V40" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W40" t="n">
         <v>123.6271901612903</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38024,7 +38024,7 @@
         <v>123.6271901612903</v>
       </c>
       <c r="X43" t="n">
-        <v>94.76768520402656</v>
+        <v>102.5563545698924</v>
       </c>
       <c r="Y43" t="n">
         <v>62.53464715053764</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>93.38475247205329</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>559.0000000000001</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>93.38475247205298</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>559</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
